--- a/research/traditional_assets/database/data/india/india_insurance_life.xlsx
+++ b/research/traditional_assets/database/data/india/india_insurance_life.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AQ8"/>
+  <dimension ref="A1:AQ9"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -579,7 +579,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -588,124 +588,124 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.278</v>
+        <v>0.188</v>
       </c>
       <c r="E2">
-        <v>-0.0619</v>
+        <v>-0.01445</v>
       </c>
       <c r="F2">
-        <v>0.214</v>
+        <v>0.2115</v>
       </c>
       <c r="G2">
-        <v>0.01494609665891684</v>
+        <v>0.003907983346819452</v>
       </c>
       <c r="H2">
-        <v>0.01494609665891684</v>
+        <v>0.003907983346819452</v>
       </c>
       <c r="I2">
-        <v>0.00917565591345668</v>
+        <v>0.02002917523571545</v>
       </c>
       <c r="J2">
-        <v>0.008125093084486733</v>
+        <v>0.01753584726993992</v>
       </c>
       <c r="K2">
-        <v>167.4</v>
+        <v>3106.9</v>
       </c>
       <c r="L2">
-        <v>0.004180411997832379</v>
+        <v>0.02534275403930986</v>
       </c>
       <c r="M2">
-        <v>127.0696</v>
+        <v>208.2932</v>
       </c>
       <c r="N2">
-        <v>0.002281231261960928</v>
+        <v>0.002142001988846418</v>
       </c>
       <c r="O2">
-        <v>0.7590776583034647</v>
+        <v>0.0670421320287103</v>
       </c>
       <c r="P2">
-        <v>127.0696</v>
+        <v>193.2932</v>
       </c>
       <c r="Q2">
-        <v>0.002281231261960928</v>
+        <v>0.001987748130186143</v>
       </c>
       <c r="R2">
-        <v>0.7590776583034647</v>
+        <v>0.062214168463742</v>
       </c>
       <c r="S2">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="T2">
-        <v>0</v>
+        <v>0.07201387275244703</v>
       </c>
       <c r="U2">
-        <v>958</v>
+        <v>4447.4</v>
       </c>
       <c r="V2">
-        <v>0.01719860256865977</v>
+        <v>0.04573524073371361</v>
       </c>
       <c r="W2">
-        <v>0.1012449286140298</v>
+        <v>0.1400204012240734</v>
       </c>
       <c r="X2">
-        <v>0.07714567077971649</v>
+        <v>0.1176213504289768</v>
       </c>
       <c r="Y2">
-        <v>0.02409925783431331</v>
+        <v>0.02239905079509664</v>
       </c>
       <c r="Z2">
-        <v>10.08211754474586</v>
+        <v>27.65986602162233</v>
       </c>
       <c r="AA2">
-        <v>0.1152942953743884</v>
+        <v>0.1001367687354921</v>
       </c>
       <c r="AB2">
-        <v>0.07665360057483231</v>
+        <v>0.1166261362286784</v>
       </c>
       <c r="AC2">
-        <v>0.0386406947995561</v>
+        <v>-0.0162313428479144</v>
       </c>
       <c r="AD2">
-        <v>1030.5</v>
+        <v>1043.6</v>
       </c>
       <c r="AE2">
-        <v>50.59476083566</v>
+        <v>54.85128071208369</v>
       </c>
       <c r="AF2">
-        <v>1081.09476083566</v>
+        <v>1098.451280712084</v>
       </c>
       <c r="AG2">
-        <v>123.0947608356601</v>
+        <v>-3348.948719287916</v>
       </c>
       <c r="AH2">
-        <v>0.01903895794333703</v>
+        <v>0.01116984837319955</v>
       </c>
       <c r="AI2">
-        <v>0.1769300505378249</v>
+        <v>0.1041378403914935</v>
       </c>
       <c r="AJ2">
-        <v>0.002204999747211678</v>
+        <v>-0.03566758107584844</v>
       </c>
       <c r="AK2">
-        <v>0.02389124973426309</v>
+        <v>-0.5489493769093154</v>
       </c>
       <c r="AL2">
-        <v>20.84</v>
+        <v>137.87</v>
       </c>
       <c r="AM2">
-        <v>20.84</v>
+        <v>137.87</v>
       </c>
       <c r="AN2">
-        <v>2.578519096805188</v>
+        <v>1.581569172434383</v>
       </c>
       <c r="AO2">
-        <v>17.54798464491363</v>
+        <v>17.76963806484369</v>
       </c>
       <c r="AP2">
-        <v>0.3080079490843443</v>
+        <v>-5.075310515992119</v>
       </c>
       <c r="AQ2">
-        <v>17.54798464491363</v>
+        <v>17.76963806484369</v>
       </c>
     </row>
     <row r="3">
@@ -716,7 +716,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Max Financial Services Limited (NSEI:MFSL)</t>
+          <t>Life Insurance Corporation of India (NSEI:LICI)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -724,98 +724,104 @@
           <t>Insurance (Life)</t>
         </is>
       </c>
+      <c r="F3">
+        <v>0.526</v>
+      </c>
       <c r="G3">
-        <v>0.01988976755331895</v>
+        <v>0.0004476774368470057</v>
       </c>
       <c r="H3">
-        <v>0.01988976755331895</v>
+        <v>0.0004476774368470057</v>
       </c>
       <c r="I3">
-        <v>0.01660022220769884</v>
+        <v>0.01921545054635563</v>
       </c>
       <c r="J3">
-        <v>0.01314184258109492</v>
+        <v>0.01325623157408361</v>
       </c>
       <c r="K3">
-        <v>40.3</v>
+        <v>2767.2</v>
       </c>
       <c r="L3">
-        <v>0.008779382611158312</v>
+        <v>0.02908011744701958</v>
       </c>
       <c r="M3">
-        <v>-0</v>
+        <v>113.85</v>
       </c>
       <c r="N3">
-        <v>-0</v>
+        <v>0.002176011314876578</v>
       </c>
       <c r="O3">
-        <v>-0</v>
+        <v>0.041142671292281</v>
       </c>
       <c r="P3">
-        <v>-0</v>
+        <v>113.85</v>
       </c>
       <c r="Q3">
-        <v>-0</v>
+        <v>0.002176011314876578</v>
       </c>
       <c r="R3">
-        <v>-0</v>
+        <v>0.041142671292281</v>
       </c>
       <c r="S3">
         <v>0</v>
       </c>
+      <c r="T3">
+        <v>0</v>
+      </c>
       <c r="U3">
-        <v>33.9</v>
+        <v>3508.5</v>
       </c>
       <c r="V3">
-        <v>0.007465644820295983</v>
+        <v>0.06705784539520838</v>
+      </c>
+      <c r="W3">
+        <v>2.344886026607915</v>
       </c>
       <c r="X3">
-        <v>0.07766138209599396</v>
+        <v>0.1167127418595986</v>
+      </c>
+      <c r="Y3">
+        <v>2.228173284748316</v>
       </c>
       <c r="AB3">
-        <v>0.07660328615887158</v>
+        <v>0.1167127418595986</v>
       </c>
       <c r="AD3">
-        <v>101.9</v>
+        <v>0</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>101.9</v>
+        <v>0</v>
       </c>
       <c r="AG3">
-        <v>68</v>
+        <v>-3508.5</v>
       </c>
       <c r="AH3">
-        <v>0.02194843517780602</v>
+        <v>0</v>
       </c>
       <c r="AI3">
-        <v>0.1508735564110157</v>
+        <v>0</v>
       </c>
       <c r="AJ3">
-        <v>0.01475438291963201</v>
+        <v>-0.07187781693026304</v>
       </c>
       <c r="AK3">
-        <v>0.1060015588464536</v>
+        <v>17.96466973886327</v>
       </c>
       <c r="AL3">
-        <v>3.59</v>
+        <v>10.7</v>
       </c>
       <c r="AM3">
-        <v>3.59</v>
-      </c>
-      <c r="AN3">
-        <v>1.248774509803922</v>
+        <v>10.7</v>
       </c>
       <c r="AO3">
-        <v>21.22562674094708</v>
-      </c>
-      <c r="AP3">
-        <v>0.8333333333333334</v>
+        <v>170.8878504672897</v>
       </c>
       <c r="AQ3">
-        <v>21.22562674094708</v>
+        <v>170.8878504672897</v>
       </c>
     </row>
     <row r="4">
@@ -826,7 +832,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>SBI Life Insurance Company Limited (BSE:540719)</t>
+          <t>SBI Life Insurance Company Limited (NSEI:SBILIFE)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -835,49 +841,49 @@
         </is>
       </c>
       <c r="D4">
-        <v>0.278</v>
+        <v>0.188</v>
       </c>
       <c r="E4">
-        <v>0.0532</v>
+        <v>0.09810000000000001</v>
       </c>
       <c r="F4">
-        <v>0.217</v>
+        <v>0.197</v>
       </c>
       <c r="G4">
-        <v>0.01952234167857053</v>
+        <v>0.02552135054617677</v>
       </c>
       <c r="H4">
-        <v>0.01952234167857053</v>
+        <v>0.02552135054617677</v>
       </c>
       <c r="I4">
-        <v>0.0153440372329403</v>
+        <v>0.02580824910962293</v>
       </c>
       <c r="J4">
-        <v>0.01403726483123384</v>
+        <v>0.02309395259309588</v>
       </c>
       <c r="K4">
-        <v>166.5</v>
+        <v>205.9</v>
       </c>
       <c r="L4">
-        <v>0.01390872866701752</v>
+        <v>0.02271874655191438</v>
       </c>
       <c r="M4">
-        <v>33.7</v>
+        <v>24.6</v>
       </c>
       <c r="N4">
-        <v>0.002098459469220519</v>
+        <v>0.001652093323125277</v>
       </c>
       <c r="O4">
-        <v>0.2024024024024024</v>
+        <v>0.1194754735308402</v>
       </c>
       <c r="P4">
-        <v>33.7</v>
+        <v>24.6</v>
       </c>
       <c r="Q4">
-        <v>0.002098459469220519</v>
+        <v>0.001652093323125277</v>
       </c>
       <c r="R4">
-        <v>0.2024024024024024</v>
+        <v>0.1194754735308402</v>
       </c>
       <c r="S4">
         <v>0</v>
@@ -886,73 +892,73 @@
         <v>0</v>
       </c>
       <c r="U4">
-        <v>340.7</v>
+        <v>405.8</v>
       </c>
       <c r="V4">
-        <v>0.02121498935203059</v>
+        <v>0.0272528240050503</v>
       </c>
       <c r="W4">
-        <v>0.1266834056151564</v>
+        <v>0.1400204012240734</v>
       </c>
       <c r="X4">
-        <v>0.07681729717427749</v>
+        <v>0.1168684053148189</v>
       </c>
       <c r="Y4">
-        <v>0.04986610844087888</v>
+        <v>0.02315199590925456</v>
       </c>
       <c r="Z4">
-        <v>11.21931449330732</v>
+        <v>7.730961571039112</v>
       </c>
       <c r="AA4">
-        <v>0.1574884887674551</v>
+        <v>0.1785384600206233</v>
       </c>
       <c r="AB4">
-        <v>0.07668204470109861</v>
+        <v>0.1166835999078093</v>
       </c>
       <c r="AC4">
-        <v>0.08080644406635644</v>
+        <v>0.06185486011281403</v>
       </c>
       <c r="AD4">
         <v>0</v>
       </c>
       <c r="AE4">
-        <v>45.99032344097488</v>
+        <v>42.4991915974367</v>
       </c>
       <c r="AF4">
-        <v>45.99032344097488</v>
+        <v>42.4991915974367</v>
       </c>
       <c r="AG4">
-        <v>-294.7096765590251</v>
+        <v>-363.3008084025633</v>
       </c>
       <c r="AH4">
-        <v>0.002855585770810979</v>
+        <v>0.002846048865790506</v>
       </c>
       <c r="AI4">
-        <v>0.03032681628763781</v>
+        <v>0.02753074681179179</v>
       </c>
       <c r="AJ4">
-        <v>-0.01869428897824988</v>
+        <v>-0.02500883386130342</v>
       </c>
       <c r="AK4">
-        <v>-0.2506481561240878</v>
+        <v>-0.3192732810474576</v>
       </c>
       <c r="AL4">
-        <v>1.12</v>
+        <v>1.23</v>
       </c>
       <c r="AM4">
-        <v>1.12</v>
+        <v>1.23</v>
       </c>
       <c r="AN4">
         <v>0</v>
       </c>
       <c r="AO4">
-        <v>163.4821428571428</v>
+        <v>188.130081300813</v>
       </c>
       <c r="AP4">
-        <v>-1.478872323158496</v>
+        <v>-1.470853475314021</v>
       </c>
       <c r="AQ4">
-        <v>163.4821428571428</v>
+        <v>188.130081300813</v>
       </c>
     </row>
     <row r="5">
@@ -963,7 +969,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>HDFC Life Insurance Company Limited (BSE:540777)</t>
+          <t>HDFC Life Insurance Company Limited (NSEI:HDFCLIFE)</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -972,43 +978,43 @@
         </is>
       </c>
       <c r="F5">
-        <v>0.127</v>
+        <v>0.226</v>
       </c>
       <c r="G5">
-        <v>0.02253234481756069</v>
+        <v>0.02850964236343977</v>
       </c>
       <c r="H5">
-        <v>0.02253234481756069</v>
+        <v>0.02850964236343977</v>
       </c>
       <c r="I5">
-        <v>0.0190520208942255</v>
+        <v>0.02866885022097748</v>
       </c>
       <c r="J5">
-        <v>0.01582440822016393</v>
+        <v>0.02539364689930567</v>
       </c>
       <c r="K5">
-        <v>156.4</v>
+        <v>176</v>
       </c>
       <c r="L5">
-        <v>0.01515724184716771</v>
+        <v>0.02408880007664618</v>
       </c>
       <c r="M5">
-        <v>54.6696</v>
+        <v>45.1332</v>
       </c>
       <c r="N5">
-        <v>0.003100765696784073</v>
+        <v>0.003069304372071514</v>
       </c>
       <c r="O5">
-        <v>0.3495498721227621</v>
+        <v>0.2564386363636364</v>
       </c>
       <c r="P5">
-        <v>54.6696</v>
+        <v>45.1332</v>
       </c>
       <c r="Q5">
-        <v>0.003100765696784073</v>
+        <v>0.003069304372071514</v>
       </c>
       <c r="R5">
-        <v>0.3495498721227621</v>
+        <v>0.2564386363636364</v>
       </c>
       <c r="S5">
         <v>0</v>
@@ -1017,73 +1023,73 @@
         <v>0</v>
       </c>
       <c r="U5">
-        <v>59</v>
+        <v>62.4</v>
       </c>
       <c r="V5">
-        <v>0.003346378537802734</v>
+        <v>0.004243541180710929</v>
       </c>
       <c r="W5">
-        <v>0.1468958392035315</v>
+        <v>0.1463982698386292</v>
       </c>
       <c r="X5">
-        <v>0.07689378488355954</v>
+        <v>0.1171779692528152</v>
       </c>
       <c r="Y5">
-        <v>0.07000205431997196</v>
+        <v>0.02922030058581397</v>
       </c>
       <c r="Z5">
-        <v>9.372201793399087</v>
+        <v>5.926426918459896</v>
       </c>
       <c r="AA5">
-        <v>0.1483095471004997</v>
+        <v>0.1504935925419108</v>
       </c>
       <c r="AB5">
-        <v>0.07667478143550734</v>
+        <v>0.1166261362286784</v>
       </c>
       <c r="AC5">
-        <v>0.07163476566499234</v>
+        <v>0.03386745631323235</v>
       </c>
       <c r="AD5">
-        <v>80.90000000000001</v>
+        <v>116.7</v>
       </c>
       <c r="AE5">
-        <v>0.8686120146707749</v>
+        <v>8.733898152361236</v>
       </c>
       <c r="AF5">
-        <v>81.76861201467078</v>
+        <v>125.4338981523612</v>
       </c>
       <c r="AG5">
-        <v>22.76861201467078</v>
+        <v>63.03389815236124</v>
       </c>
       <c r="AH5">
-        <v>0.004616365391868026</v>
+        <v>0.008458042187197557</v>
       </c>
       <c r="AI5">
-        <v>0.06368427642975472</v>
+        <v>0.05420104607944132</v>
       </c>
       <c r="AJ5">
-        <v>0.001289730964252873</v>
+        <v>0.004268352787711567</v>
       </c>
       <c r="AK5">
-        <v>0.01858709830713449</v>
+        <v>0.0279922503183209</v>
       </c>
       <c r="AL5">
-        <v>7.89</v>
+        <v>8.83</v>
       </c>
       <c r="AM5">
-        <v>7.89</v>
+        <v>8.83</v>
       </c>
       <c r="AN5">
-        <v>0.4062019863226921</v>
+        <v>0.5470910880877596</v>
       </c>
       <c r="AO5">
-        <v>24.86692015209125</v>
+        <v>23.49943374858437</v>
       </c>
       <c r="AP5">
-        <v>0.1143220695447464</v>
+        <v>0.2955037183083833</v>
       </c>
       <c r="AQ5">
-        <v>24.86692015209125</v>
+        <v>23.49943374858437</v>
       </c>
     </row>
     <row r="6">
@@ -1094,7 +1100,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>ICICI Prudential Life Insurance Company Limited (BSE:540133)</t>
+          <t>Max Financial Services Limited (NSEI:MFSL)</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1102,125 +1108,116 @@
           <t>Insurance (Life)</t>
         </is>
       </c>
-      <c r="D6">
-        <v>0.234</v>
-      </c>
-      <c r="E6">
-        <v>-0.177</v>
-      </c>
-      <c r="F6">
-        <v>0.214</v>
-      </c>
       <c r="G6">
-        <v>0.01483535760228545</v>
+        <v>0.01863531291915185</v>
       </c>
       <c r="H6">
-        <v>0.01483535760228545</v>
+        <v>0.01863531291915185</v>
       </c>
       <c r="I6">
-        <v>0.009478071365669622</v>
+        <v>0.0160668930681202</v>
       </c>
       <c r="J6">
-        <v>0.007354426358118302</v>
+        <v>0.01435138416682291</v>
       </c>
       <c r="K6">
-        <v>84.59999999999999</v>
+        <v>36.9</v>
       </c>
       <c r="L6">
-        <v>0.007066842641629216</v>
+        <v>0.01053052138922976</v>
       </c>
       <c r="M6">
-        <v>38.7</v>
+        <v>15</v>
       </c>
       <c r="N6">
-        <v>0.003575553194438029</v>
+        <v>0.00530935862947756</v>
       </c>
       <c r="O6">
-        <v>0.4574468085106383</v>
+        <v>0.4065040650406504</v>
       </c>
       <c r="P6">
-        <v>38.7</v>
+        <v>-0</v>
       </c>
       <c r="Q6">
-        <v>0.003575553194438029</v>
+        <v>-0</v>
       </c>
       <c r="R6">
-        <v>0.4574468085106383</v>
+        <v>-0</v>
       </c>
       <c r="S6">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="T6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U6">
-        <v>123.5</v>
+        <v>54.2</v>
       </c>
       <c r="V6">
-        <v>0.01141035709336167</v>
+        <v>0.01918448251451225</v>
       </c>
       <c r="W6">
-        <v>0.07580645161290323</v>
+        <v>0.07306930693069306</v>
       </c>
       <c r="X6">
-        <v>0.07734533380745194</v>
+        <v>0.1186122992924491</v>
       </c>
       <c r="Y6">
-        <v>-0.001538882194548716</v>
+        <v>-0.04554299236175602</v>
       </c>
       <c r="Z6">
-        <v>11.18769019387244</v>
+        <v>6.977499004380725</v>
       </c>
       <c r="AA6">
-        <v>0.08227904364827714</v>
+        <v>0.1001367687354921</v>
       </c>
       <c r="AB6">
-        <v>0.07663241971415728</v>
+        <v>0.1163681115834065</v>
       </c>
       <c r="AC6">
-        <v>0.005646623934119854</v>
+        <v>-0.0162313428479144</v>
       </c>
       <c r="AD6">
-        <v>161.8</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="AE6">
-        <v>1.751082265113389</v>
+        <v>0</v>
       </c>
       <c r="AF6">
-        <v>163.5510822651134</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="AG6">
-        <v>40.05108226511339</v>
+        <v>44.2</v>
       </c>
       <c r="AH6">
-        <v>0.01488580339169547</v>
+        <v>0.03365713503899302</v>
       </c>
       <c r="AI6">
-        <v>0.1218029792902612</v>
+        <v>0.1515945154829764</v>
       </c>
       <c r="AJ6">
-        <v>0.003686739442915429</v>
+        <v>0.01540391719523246</v>
       </c>
       <c r="AK6">
-        <v>0.03284892082335237</v>
+        <v>0.07429820137838292</v>
       </c>
       <c r="AL6">
-        <v>4.43</v>
+        <v>5</v>
       </c>
       <c r="AM6">
-        <v>4.43</v>
+        <v>5</v>
       </c>
       <c r="AN6">
-        <v>1.351531958969561</v>
+        <v>1.532710280373832</v>
       </c>
       <c r="AO6">
-        <v>25.59819413092551</v>
+        <v>11.26</v>
       </c>
       <c r="AP6">
-        <v>0.3345507890767599</v>
+        <v>0.6884735202492211</v>
       </c>
       <c r="AQ6">
-        <v>25.59819413092551</v>
+        <v>11.26</v>
       </c>
     </row>
     <row r="7">
@@ -1231,7 +1228,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Religare Enterprises Limited (BSE:532915)</t>
+          <t>Religare Enterprises Limited (NSEI:RELIGARE)</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1240,22 +1237,22 @@
         </is>
       </c>
       <c r="G7">
-        <v>0</v>
+        <v>-0.07227227227227227</v>
       </c>
       <c r="H7">
-        <v>0</v>
+        <v>-0.07227227227227227</v>
       </c>
       <c r="I7">
-        <v>0</v>
+        <v>0.05785785785785785</v>
       </c>
       <c r="J7">
-        <v>0</v>
+        <v>0.05785785785785785</v>
       </c>
       <c r="K7">
-        <v>-119.3</v>
+        <v>-140.7</v>
       </c>
       <c r="L7">
-        <v>-0.4061967994552264</v>
+        <v>-0.2816816816816817</v>
       </c>
       <c r="M7">
         <v>-0</v>
@@ -1279,61 +1276,73 @@
         <v>0</v>
       </c>
       <c r="U7">
-        <v>328.6</v>
+        <v>313.1</v>
       </c>
       <c r="V7">
-        <v>0.5830376153300213</v>
+        <v>0.4614591009579956</v>
       </c>
       <c r="W7">
-        <v>-5.935323383084577</v>
+        <v>7.564516129032257</v>
       </c>
       <c r="X7">
-        <v>0.1265950944951125</v>
+        <v>0.1663162305863353</v>
       </c>
       <c r="Y7">
-        <v>-6.061918477579689</v>
+        <v>7.398199898445922</v>
       </c>
       <c r="Z7">
-        <v>0.5868366368286445</v>
+        <v>1.644227920603049</v>
       </c>
       <c r="AA7">
-        <v>0</v>
+        <v>0.09513150531617239</v>
       </c>
       <c r="AB7">
-        <v>0.07621499219127517</v>
+        <v>0.1144029313088499</v>
       </c>
       <c r="AC7">
-        <v>-0.07621499219127517</v>
+        <v>-0.01927142599267749</v>
       </c>
       <c r="AD7">
-        <v>652.3</v>
+        <v>617.1</v>
       </c>
       <c r="AE7">
         <v>0</v>
       </c>
       <c r="AF7">
-        <v>652.3</v>
+        <v>617.1</v>
       </c>
       <c r="AG7">
-        <v>323.6999999999999</v>
+        <v>304</v>
       </c>
       <c r="AH7">
-        <v>0.5364750390657126</v>
+        <v>0.4763044149428837</v>
       </c>
       <c r="AI7">
-        <v>0.9554709242712759</v>
+        <v>1.173416999429549</v>
       </c>
       <c r="AJ7">
-        <v>0.3648146061084188</v>
+        <v>0.3094147582697201</v>
       </c>
       <c r="AK7">
-        <v>0.9141485456085852</v>
+        <v>1.428571428571429</v>
       </c>
       <c r="AL7">
-        <v>0</v>
+        <v>93.7</v>
       </c>
       <c r="AM7">
-        <v>0</v>
+        <v>93.7</v>
+      </c>
+      <c r="AN7">
+        <v>20.10097719869707</v>
+      </c>
+      <c r="AO7">
+        <v>0.3084311632870864</v>
+      </c>
+      <c r="AP7">
+        <v>9.90228013029316</v>
+      </c>
+      <c r="AQ7">
+        <v>0.3084311632870864</v>
       </c>
     </row>
     <row r="8">
@@ -1344,124 +1353,255 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
+          <t>ICICI Prudential Life Insurance Company Limited (NSEI:ICICIPRULI)</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Insurance (Life)</t>
+        </is>
+      </c>
+      <c r="D8">
+        <v>0.0421</v>
+      </c>
+      <c r="E8">
+        <v>-0.127</v>
+      </c>
+      <c r="F8">
+        <v>0.126</v>
+      </c>
+      <c r="G8">
+        <v>0.02535803210369246</v>
+      </c>
+      <c r="H8">
+        <v>0.02535803210369246</v>
+      </c>
+      <c r="I8">
+        <v>0.0260739044736731</v>
+      </c>
+      <c r="J8">
+        <v>0.01994444949187076</v>
+      </c>
+      <c r="K8">
+        <v>105.1</v>
+      </c>
+      <c r="L8">
+        <v>0.01855939536279998</v>
+      </c>
+      <c r="M8">
+        <v>9.710000000000001</v>
+      </c>
+      <c r="N8">
+        <v>0.001237794151390766</v>
+      </c>
+      <c r="O8">
+        <v>0.09238820171265463</v>
+      </c>
+      <c r="P8">
+        <v>9.710000000000001</v>
+      </c>
+      <c r="Q8">
+        <v>0.001237794151390766</v>
+      </c>
+      <c r="R8">
+        <v>0.09238820171265463</v>
+      </c>
+      <c r="S8">
+        <v>0</v>
+      </c>
+      <c r="T8">
+        <v>0</v>
+      </c>
+      <c r="U8">
+        <v>66.5</v>
+      </c>
+      <c r="V8">
+        <v>0.008477169007980012</v>
+      </c>
+      <c r="W8">
+        <v>0.0891282225237449</v>
+      </c>
+      <c r="X8">
+        <v>0.1177468123936177</v>
+      </c>
+      <c r="Y8">
+        <v>-0.02861858986987276</v>
+      </c>
+      <c r="Z8">
+        <v>4.646537593256243</v>
+      </c>
+      <c r="AA8">
+        <v>0.09267263434077787</v>
+      </c>
+      <c r="AB8">
+        <v>0.1165222121597169</v>
+      </c>
+      <c r="AC8">
+        <v>-0.02384957781893904</v>
+      </c>
+      <c r="AD8">
+        <v>147.5</v>
+      </c>
+      <c r="AE8">
+        <v>1.235431780183103</v>
+      </c>
+      <c r="AF8">
+        <v>148.7354317801831</v>
+      </c>
+      <c r="AG8">
+        <v>82.23543178018309</v>
+      </c>
+      <c r="AH8">
+        <v>0.01860743028358794</v>
+      </c>
+      <c r="AI8">
+        <v>0.1116938076522548</v>
+      </c>
+      <c r="AJ8">
+        <v>0.01037430794267353</v>
+      </c>
+      <c r="AK8">
+        <v>0.06500128738349292</v>
+      </c>
+      <c r="AL8">
+        <v>10.1</v>
+      </c>
+      <c r="AM8">
+        <v>10.1</v>
+      </c>
+      <c r="AN8">
+        <v>0.9646764900164158</v>
+      </c>
+      <c r="AO8">
+        <v>14.6039603960396</v>
+      </c>
+      <c r="AP8">
+        <v>0.537834492777569</v>
+      </c>
+      <c r="AQ8">
+        <v>14.6039603960396</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
           <t>Star Health and Allied Insurance Company Limited (NSEI:STARHEALTH)</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="C9" t="inlineStr">
         <is>
           <t>Insurance (Life)</t>
         </is>
       </c>
-      <c r="D8">
-        <v>0.333</v>
-      </c>
-      <c r="G8">
-        <v>-0.151929707485263</v>
-      </c>
-      <c r="H8">
-        <v>-0.151929707485263</v>
-      </c>
-      <c r="I8">
-        <v>-0.2252329536458461</v>
-      </c>
-      <c r="J8">
-        <v>-0.2252329536458461</v>
-      </c>
-      <c r="K8">
-        <v>-161.1</v>
-      </c>
-      <c r="L8">
-        <v>-0.1791791791791792</v>
-      </c>
-      <c r="M8">
+      <c r="D9">
+        <v>0.379</v>
+      </c>
+      <c r="G9">
+        <v>-0.1254994292237443</v>
+      </c>
+      <c r="H9">
+        <v>-0.1254994292237443</v>
+      </c>
+      <c r="I9">
+        <v>-0.0351288183764416</v>
+      </c>
+      <c r="J9">
+        <v>-0.0351288183764416</v>
+      </c>
+      <c r="K9">
+        <v>-43.5</v>
+      </c>
+      <c r="L9">
+        <v>-0.03103595890410959</v>
+      </c>
+      <c r="M9">
         <v>-0</v>
       </c>
-      <c r="N8">
+      <c r="N9">
         <v>-0</v>
       </c>
-      <c r="O8">
-        <v>0</v>
-      </c>
-      <c r="P8">
+      <c r="O9">
+        <v>0</v>
+      </c>
+      <c r="P9">
         <v>-0</v>
       </c>
-      <c r="Q8">
+      <c r="Q9">
         <v>-0</v>
       </c>
-      <c r="R8">
-        <v>0</v>
-      </c>
-      <c r="S8">
-        <v>0</v>
-      </c>
-      <c r="U8">
-        <v>72.3</v>
-      </c>
-      <c r="V8">
-        <v>0.01188382452045563</v>
-      </c>
-      <c r="W8">
-        <v>-0.5883856829802775</v>
-      </c>
-      <c r="X8">
-        <v>0.07694600775198103</v>
-      </c>
-      <c r="Y8">
-        <v>-0.6653316907322585</v>
-      </c>
-      <c r="Z8">
-        <v>3.854088304253834</v>
-      </c>
-      <c r="AA8">
-        <v>-0.8680676923790012</v>
-      </c>
-      <c r="AB8">
-        <v>0.07670103555348776</v>
-      </c>
-      <c r="AC8">
-        <v>-0.9447687279324889</v>
-      </c>
-      <c r="AD8">
-        <v>33.6</v>
-      </c>
-      <c r="AE8">
-        <v>1.984743114900958</v>
-      </c>
-      <c r="AF8">
-        <v>35.58474311490096</v>
-      </c>
-      <c r="AG8">
-        <v>-36.71525688509904</v>
-      </c>
-      <c r="AH8">
-        <v>0.005814990086369239</v>
-      </c>
-      <c r="AI8">
-        <v>0.05843289756798876</v>
-      </c>
-      <c r="AJ8">
-        <v>-0.00607146274585073</v>
-      </c>
-      <c r="AK8">
-        <v>-0.06841121786321867</v>
-      </c>
-      <c r="AL8">
-        <v>3.81</v>
-      </c>
-      <c r="AM8">
-        <v>3.81</v>
-      </c>
-      <c r="AN8">
-        <v>-0.1679076507920644</v>
-      </c>
-      <c r="AO8">
-        <v>-53.33333333333333</v>
-      </c>
-      <c r="AP8">
-        <v>0.1834753729703615</v>
-      </c>
-      <c r="AQ8">
-        <v>-53.33333333333333</v>
+      <c r="R9">
+        <v>0</v>
+      </c>
+      <c r="S9">
+        <v>0</v>
+      </c>
+      <c r="U9">
+        <v>36.9</v>
+      </c>
+      <c r="V9">
+        <v>0.009274619212788418</v>
+      </c>
+      <c r="X9">
+        <v>0.1176213504289768</v>
+      </c>
+      <c r="Z9">
+        <v>588.2256211738376</v>
+      </c>
+      <c r="AA9">
+        <v>-20.66367101058528</v>
+      </c>
+      <c r="AB9">
+        <v>0.1166332749371387</v>
+      </c>
+      <c r="AC9">
+        <v>-20.78030428552242</v>
+      </c>
+      <c r="AD9">
+        <v>63.9</v>
+      </c>
+      <c r="AE9">
+        <v>2.382759182102656</v>
+      </c>
+      <c r="AF9">
+        <v>66.28275918210265</v>
+      </c>
+      <c r="AG9">
+        <v>29.38275918210265</v>
+      </c>
+      <c r="AH9">
+        <v>0.0163868183896399</v>
+      </c>
+      <c r="AI9">
+        <v>0.07616232595989333</v>
+      </c>
+      <c r="AJ9">
+        <v>0.007331059275339474</v>
+      </c>
+      <c r="AK9">
+        <v>0.03525721987690199</v>
+      </c>
+      <c r="AL9">
+        <v>8.31</v>
+      </c>
+      <c r="AM9">
+        <v>8.31</v>
+      </c>
+      <c r="AN9">
+        <v>-1.324077911313717</v>
+      </c>
+      <c r="AO9">
+        <v>-6.040914560770156</v>
+      </c>
+      <c r="AP9">
+        <v>-0.6088429171591929</v>
+      </c>
+      <c r="AQ9">
+        <v>-6.040914560770156</v>
       </c>
     </row>
   </sheetData>

--- a/research/traditional_assets/database/data/india/india_insurance_life.xlsx
+++ b/research/traditional_assets/database/data/india/india_insurance_life.xlsx
@@ -588,124 +588,124 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.188</v>
+        <v>0.23</v>
       </c>
       <c r="E2">
-        <v>-0.01445</v>
+        <v>0.04455000000000001</v>
       </c>
       <c r="F2">
-        <v>0.2115</v>
+        <v>0.05445000000000001</v>
       </c>
       <c r="G2">
-        <v>0.003907983346819452</v>
+        <v>0.03753718263754788</v>
       </c>
       <c r="H2">
-        <v>0.003907983346819452</v>
+        <v>0.03753718263754788</v>
       </c>
       <c r="I2">
-        <v>0.02002917523571545</v>
+        <v>0.02948959751173374</v>
       </c>
       <c r="J2">
-        <v>0.01753584726993992</v>
+        <v>0.02661321153954289</v>
       </c>
       <c r="K2">
-        <v>3106.9</v>
+        <v>5805.900000000001</v>
       </c>
       <c r="L2">
-        <v>0.02534275403930986</v>
+        <v>0.04315415798885971</v>
       </c>
       <c r="M2">
-        <v>208.2932</v>
+        <v>204.8211</v>
       </c>
       <c r="N2">
-        <v>0.002142001988846418</v>
+        <v>0.001749439903790718</v>
       </c>
       <c r="O2">
-        <v>0.0670421320287103</v>
+        <v>0.03527809641915982</v>
       </c>
       <c r="P2">
-        <v>193.2932</v>
+        <v>204.1661</v>
       </c>
       <c r="Q2">
-        <v>0.001987748130186143</v>
+        <v>0.001743845347678174</v>
       </c>
       <c r="R2">
-        <v>0.062214168463742</v>
+        <v>0.03516528014605832</v>
       </c>
       <c r="S2">
-        <v>15</v>
+        <v>0.655</v>
       </c>
       <c r="T2">
-        <v>0.07201387275244703</v>
+        <v>0.003197912715047424</v>
       </c>
       <c r="U2">
-        <v>4447.4</v>
+        <v>5285.2</v>
       </c>
       <c r="V2">
-        <v>0.04573524073371361</v>
+        <v>0.04514251597865015</v>
       </c>
       <c r="W2">
-        <v>0.1400204012240734</v>
+        <v>0.1085820895522388</v>
       </c>
       <c r="X2">
-        <v>0.1176213504289768</v>
+        <v>0.1002842032305827</v>
       </c>
       <c r="Y2">
-        <v>0.02239905079509664</v>
+        <v>0.008297886321656067</v>
       </c>
       <c r="Z2">
-        <v>27.65986602162233</v>
+        <v>22.12818957380804</v>
       </c>
       <c r="AA2">
-        <v>0.1001367687354921</v>
+        <v>0.1711079146456564</v>
       </c>
       <c r="AB2">
-        <v>0.1166261362286784</v>
+        <v>0.09955923925633199</v>
       </c>
       <c r="AC2">
-        <v>-0.0162313428479144</v>
+        <v>0.07168863716919092</v>
       </c>
       <c r="AD2">
-        <v>1043.6</v>
+        <v>494.3</v>
       </c>
       <c r="AE2">
-        <v>54.85128071208369</v>
+        <v>44.55418103929251</v>
       </c>
       <c r="AF2">
-        <v>1098.451280712084</v>
+        <v>538.8541810392925</v>
       </c>
       <c r="AG2">
-        <v>-3348.948719287916</v>
+        <v>-4746.345818960707</v>
       </c>
       <c r="AH2">
-        <v>0.01116984837319955</v>
+        <v>0.00458143287922482</v>
       </c>
       <c r="AI2">
-        <v>0.1041378403914935</v>
+        <v>0.03766195172325242</v>
       </c>
       <c r="AJ2">
-        <v>-0.03566758107584844</v>
+        <v>-0.04225293064783148</v>
       </c>
       <c r="AK2">
-        <v>-0.5489493769093154</v>
+        <v>-0.5260592876088154</v>
       </c>
       <c r="AL2">
-        <v>137.87</v>
+        <v>79.32000000000001</v>
       </c>
       <c r="AM2">
-        <v>137.87</v>
+        <v>79.32000000000001</v>
       </c>
       <c r="AN2">
-        <v>1.581569172434383</v>
+        <v>0.121739772923183</v>
       </c>
       <c r="AO2">
-        <v>17.76963806484369</v>
+        <v>49.95587493696419</v>
       </c>
       <c r="AP2">
-        <v>-5.075310515992119</v>
+        <v>-1.168964317651579</v>
       </c>
       <c r="AQ2">
-        <v>17.76963806484369</v>
+        <v>49.95587493696419</v>
       </c>
     </row>
     <row r="3">
@@ -725,43 +725,43 @@
         </is>
       </c>
       <c r="F3">
-        <v>0.526</v>
+        <v>-0.0839</v>
       </c>
       <c r="G3">
-        <v>0.0004476774368470057</v>
+        <v>0.04407249069276271</v>
       </c>
       <c r="H3">
-        <v>0.0004476774368470057</v>
+        <v>0.04407249069276271</v>
       </c>
       <c r="I3">
-        <v>0.01921545054635563</v>
+        <v>0.03310594464941959</v>
       </c>
       <c r="J3">
-        <v>0.01325623157408361</v>
+        <v>0.03214506280500441</v>
       </c>
       <c r="K3">
-        <v>2767.2</v>
+        <v>4733.1</v>
       </c>
       <c r="L3">
-        <v>0.02908011744701958</v>
+        <v>0.0493166357033229</v>
       </c>
       <c r="M3">
-        <v>113.85</v>
+        <v>114.2</v>
       </c>
       <c r="N3">
-        <v>0.002176011314876578</v>
+        <v>0.001750054784989986</v>
       </c>
       <c r="O3">
-        <v>0.041142671292281</v>
+        <v>0.02412794996936468</v>
       </c>
       <c r="P3">
-        <v>113.85</v>
+        <v>114.2</v>
       </c>
       <c r="Q3">
-        <v>0.002176011314876578</v>
+        <v>0.001750054784989986</v>
       </c>
       <c r="R3">
-        <v>0.041142671292281</v>
+        <v>0.02412794996936468</v>
       </c>
       <c r="S3">
         <v>0</v>
@@ -770,22 +770,22 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>3508.5</v>
+        <v>4475.9</v>
       </c>
       <c r="V3">
-        <v>0.06705784539520838</v>
+        <v>0.06859080746179226</v>
       </c>
       <c r="W3">
-        <v>2.344886026607915</v>
+        <v>1.434446599587829</v>
       </c>
       <c r="X3">
-        <v>0.1167127418595986</v>
+        <v>0.09963017816409649</v>
       </c>
       <c r="Y3">
-        <v>2.228173284748316</v>
+        <v>1.334816421423733</v>
       </c>
       <c r="AB3">
-        <v>0.1167127418595986</v>
+        <v>0.09963017816409649</v>
       </c>
       <c r="AD3">
         <v>0</v>
@@ -797,7 +797,7 @@
         <v>0</v>
       </c>
       <c r="AG3">
-        <v>-3508.5</v>
+        <v>-4475.9</v>
       </c>
       <c r="AH3">
         <v>0</v>
@@ -806,22 +806,28 @@
         <v>0</v>
       </c>
       <c r="AJ3">
-        <v>-0.07187781693026304</v>
+        <v>-0.07364196962118619</v>
       </c>
       <c r="AK3">
-        <v>17.96466973886327</v>
+        <v>-1.488592523613143</v>
       </c>
       <c r="AL3">
-        <v>10.7</v>
+        <v>9.32</v>
       </c>
       <c r="AM3">
-        <v>10.7</v>
+        <v>9.32</v>
+      </c>
+      <c r="AN3">
+        <v>0</v>
       </c>
       <c r="AO3">
-        <v>170.8878504672897</v>
+        <v>340.912017167382</v>
+      </c>
+      <c r="AP3">
+        <v>-1.383457484622755</v>
       </c>
       <c r="AQ3">
-        <v>170.8878504672897</v>
+        <v>340.912017167382</v>
       </c>
     </row>
     <row r="4">
@@ -832,7 +838,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>SBI Life Insurance Company Limited (NSEI:SBILIFE)</t>
+          <t>Religare Enterprises Limited (NSEI:RELIGARE)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -840,125 +846,113 @@
           <t>Insurance (Life)</t>
         </is>
       </c>
-      <c r="D4">
-        <v>0.188</v>
-      </c>
-      <c r="E4">
-        <v>0.09810000000000001</v>
-      </c>
-      <c r="F4">
-        <v>0.197</v>
-      </c>
       <c r="G4">
-        <v>0.02552135054617677</v>
+        <v>0.08101071975497702</v>
       </c>
       <c r="H4">
-        <v>0.02552135054617677</v>
+        <v>0.08101071975497702</v>
       </c>
       <c r="I4">
-        <v>0.02580824910962293</v>
+        <v>0.1052067381316999</v>
       </c>
       <c r="J4">
-        <v>0.02309395259309588</v>
+        <v>0.1024759621419426</v>
       </c>
       <c r="K4">
-        <v>205.9</v>
+        <v>415.6</v>
       </c>
       <c r="L4">
-        <v>0.02271874655191438</v>
+        <v>0.636447166921899</v>
       </c>
       <c r="M4">
-        <v>24.6</v>
+        <v>-0</v>
       </c>
       <c r="N4">
-        <v>0.001652093323125277</v>
+        <v>-0</v>
       </c>
       <c r="O4">
-        <v>0.1194754735308402</v>
+        <v>-0</v>
       </c>
       <c r="P4">
-        <v>24.6</v>
+        <v>-0</v>
       </c>
       <c r="Q4">
-        <v>0.001652093323125277</v>
+        <v>-0</v>
       </c>
       <c r="R4">
-        <v>0.1194754735308402</v>
+        <v>-0</v>
       </c>
       <c r="S4">
         <v>0</v>
       </c>
-      <c r="T4">
-        <v>0</v>
-      </c>
       <c r="U4">
-        <v>405.8</v>
+        <v>124.2</v>
       </c>
       <c r="V4">
-        <v>0.0272528240050503</v>
+        <v>0.144217371110079</v>
       </c>
       <c r="W4">
-        <v>0.1400204012240734</v>
+        <v>-2.579764121663563</v>
       </c>
       <c r="X4">
-        <v>0.1168684053148189</v>
+        <v>0.1036697484023741</v>
       </c>
       <c r="Y4">
-        <v>0.02315199590925456</v>
+        <v>-2.683433870065937</v>
       </c>
       <c r="Z4">
-        <v>7.730961571039112</v>
+        <v>4.608002258132808</v>
       </c>
       <c r="AA4">
-        <v>0.1785384600206233</v>
+        <v>0.4722094649544037</v>
       </c>
       <c r="AB4">
-        <v>0.1166835999078093</v>
+        <v>0.09938572752367895</v>
       </c>
       <c r="AC4">
-        <v>0.06185486011281403</v>
+        <v>0.3728237374307247</v>
       </c>
       <c r="AD4">
-        <v>0</v>
+        <v>81.7</v>
       </c>
       <c r="AE4">
-        <v>42.4991915974367</v>
+        <v>0</v>
       </c>
       <c r="AF4">
-        <v>42.4991915974367</v>
+        <v>81.7</v>
       </c>
       <c r="AG4">
-        <v>-363.3008084025633</v>
+        <v>-42.5</v>
       </c>
       <c r="AH4">
-        <v>0.002846048865790506</v>
+        <v>0.08664757662530491</v>
       </c>
       <c r="AI4">
-        <v>0.02753074681179179</v>
+        <v>0.1876435461644465</v>
       </c>
       <c r="AJ4">
-        <v>-0.02500883386130342</v>
+        <v>-0.05191156711860266</v>
       </c>
       <c r="AK4">
-        <v>-0.3192732810474576</v>
+        <v>-0.1365681233933162</v>
       </c>
       <c r="AL4">
-        <v>1.23</v>
+        <v>35</v>
       </c>
       <c r="AM4">
-        <v>1.23</v>
+        <v>35</v>
       </c>
       <c r="AN4">
-        <v>0</v>
+        <v>1.134722222222222</v>
       </c>
       <c r="AO4">
-        <v>188.130081300813</v>
+        <v>1.962857142857143</v>
       </c>
       <c r="AP4">
-        <v>-1.470853475314021</v>
+        <v>-0.5902777777777778</v>
       </c>
       <c r="AQ4">
-        <v>188.130081300813</v>
+        <v>1.962857142857143</v>
       </c>
     </row>
     <row r="5">
@@ -969,7 +963,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>HDFC Life Insurance Company Limited (NSEI:HDFCLIFE)</t>
+          <t>SBI Life Insurance Company Limited (NSEI:SBILIFE)</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -977,44 +971,50 @@
           <t>Insurance (Life)</t>
         </is>
       </c>
+      <c r="D5">
+        <v>0.235</v>
+      </c>
+      <c r="E5">
+        <v>0.05110000000000001</v>
+      </c>
       <c r="F5">
-        <v>0.226</v>
+        <v>0.145</v>
       </c>
       <c r="G5">
-        <v>0.02850964236343977</v>
+        <v>0.01905101676774884</v>
       </c>
       <c r="H5">
-        <v>0.02850964236343977</v>
+        <v>0.01905101676774884</v>
       </c>
       <c r="I5">
-        <v>0.02866885022097748</v>
+        <v>0.01965064534969759</v>
       </c>
       <c r="J5">
-        <v>0.02539364689930567</v>
+        <v>0.01787668475185866</v>
       </c>
       <c r="K5">
-        <v>176</v>
+        <v>221.7</v>
       </c>
       <c r="L5">
-        <v>0.02408880007664618</v>
+        <v>0.01757640623141872</v>
       </c>
       <c r="M5">
-        <v>45.1332</v>
+        <v>30.1</v>
       </c>
       <c r="N5">
-        <v>0.003069304372071514</v>
+        <v>0.001747297783660154</v>
       </c>
       <c r="O5">
-        <v>0.2564386363636364</v>
+        <v>0.1357690572846189</v>
       </c>
       <c r="P5">
-        <v>45.1332</v>
+        <v>30.1</v>
       </c>
       <c r="Q5">
-        <v>0.003069304372071514</v>
+        <v>0.001747297783660154</v>
       </c>
       <c r="R5">
-        <v>0.2564386363636364</v>
+        <v>0.1357690572846189</v>
       </c>
       <c r="S5">
         <v>0</v>
@@ -1023,73 +1023,73 @@
         <v>0</v>
       </c>
       <c r="U5">
-        <v>62.4</v>
+        <v>421.1</v>
       </c>
       <c r="V5">
-        <v>0.004243541180710929</v>
+        <v>0.02444475404316581</v>
       </c>
       <c r="W5">
-        <v>0.1463982698386292</v>
+        <v>0.1476818545163869</v>
       </c>
       <c r="X5">
-        <v>0.1171779692528152</v>
+        <v>0.09972703146021458</v>
       </c>
       <c r="Y5">
-        <v>0.02922030058581397</v>
+        <v>0.0479548230561723</v>
       </c>
       <c r="Z5">
-        <v>5.926426918459896</v>
+        <v>11.11730110567461</v>
       </c>
       <c r="AA5">
-        <v>0.1504935925419108</v>
+        <v>0.1987404871576346</v>
       </c>
       <c r="AB5">
-        <v>0.1166261362286784</v>
+        <v>0.09961030299480744</v>
       </c>
       <c r="AC5">
-        <v>0.03386745631323235</v>
+        <v>0.09913018416282721</v>
       </c>
       <c r="AD5">
-        <v>116.7</v>
+        <v>0</v>
       </c>
       <c r="AE5">
-        <v>8.733898152361236</v>
+        <v>39.18292440794728</v>
       </c>
       <c r="AF5">
-        <v>125.4338981523612</v>
+        <v>39.18292440794728</v>
       </c>
       <c r="AG5">
-        <v>63.03389815236124</v>
+        <v>-381.9170755920528</v>
       </c>
       <c r="AH5">
-        <v>0.008458042187197557</v>
+        <v>0.002269397488633773</v>
       </c>
       <c r="AI5">
-        <v>0.05420104607944132</v>
+        <v>0.02277437564306598</v>
       </c>
       <c r="AJ5">
-        <v>0.004268352787711567</v>
+        <v>-0.02267285631352876</v>
       </c>
       <c r="AK5">
-        <v>0.0279922503183209</v>
+        <v>-0.2939218827783734</v>
       </c>
       <c r="AL5">
-        <v>8.83</v>
+        <v>1.21</v>
       </c>
       <c r="AM5">
-        <v>8.83</v>
+        <v>1.21</v>
       </c>
       <c r="AN5">
-        <v>0.5470910880877596</v>
+        <v>0</v>
       </c>
       <c r="AO5">
-        <v>23.49943374858437</v>
+        <v>202.396694214876</v>
       </c>
       <c r="AP5">
-        <v>0.2955037183083833</v>
+        <v>-1.459927658991027</v>
       </c>
       <c r="AQ5">
-        <v>23.49943374858437</v>
+        <v>202.396694214876</v>
       </c>
     </row>
     <row r="6">
@@ -1109,31 +1109,31 @@
         </is>
       </c>
       <c r="G6">
-        <v>0.01863531291915185</v>
+        <v>0.01664454646330584</v>
       </c>
       <c r="H6">
-        <v>0.01863531291915185</v>
+        <v>0.01664454646330584</v>
       </c>
       <c r="I6">
-        <v>0.0160668930681202</v>
+        <v>0.01875503143969887</v>
       </c>
       <c r="J6">
-        <v>0.01435138416682291</v>
+        <v>0.01713647943069029</v>
       </c>
       <c r="K6">
-        <v>36.9</v>
+        <v>61</v>
       </c>
       <c r="L6">
-        <v>0.01053052138922976</v>
+        <v>0.01327212201649224</v>
       </c>
       <c r="M6">
-        <v>15</v>
+        <v>0.655</v>
       </c>
       <c r="N6">
-        <v>0.00530935862947756</v>
+        <v>0.0001661087441671739</v>
       </c>
       <c r="O6">
-        <v>0.4065040650406504</v>
+        <v>0.01073770491803279</v>
       </c>
       <c r="P6">
         <v>-0</v>
@@ -1145,79 +1145,79 @@
         <v>-0</v>
       </c>
       <c r="S6">
-        <v>15</v>
+        <v>0.655</v>
       </c>
       <c r="T6">
         <v>1</v>
       </c>
       <c r="U6">
-        <v>54.2</v>
+        <v>84.7</v>
       </c>
       <c r="V6">
-        <v>0.01918448251451225</v>
+        <v>0.02148001623047271</v>
       </c>
       <c r="W6">
-        <v>0.07306930693069306</v>
+        <v>0.1269246774864752</v>
       </c>
       <c r="X6">
-        <v>0.1186122992924491</v>
+        <v>0.1006808840463131</v>
       </c>
       <c r="Y6">
-        <v>-0.04554299236175602</v>
+        <v>0.02624379344016212</v>
       </c>
       <c r="Z6">
-        <v>6.977499004380725</v>
+        <v>9.985009776232893</v>
       </c>
       <c r="AA6">
-        <v>0.1001367687354921</v>
+        <v>0.1711079146456564</v>
       </c>
       <c r="AB6">
-        <v>0.1163681115834065</v>
+        <v>0.09941927747646549</v>
       </c>
       <c r="AC6">
-        <v>-0.0162313428479144</v>
+        <v>0.07168863716919092</v>
       </c>
       <c r="AD6">
-        <v>98.40000000000001</v>
+        <v>97.3</v>
       </c>
       <c r="AE6">
         <v>0</v>
       </c>
       <c r="AF6">
-        <v>98.40000000000001</v>
+        <v>97.3</v>
       </c>
       <c r="AG6">
-        <v>44.2</v>
+        <v>12.59999999999999</v>
       </c>
       <c r="AH6">
-        <v>0.03365713503899302</v>
+        <v>0.02408117807202079</v>
       </c>
       <c r="AI6">
-        <v>0.1515945154829764</v>
+        <v>0.1601646090534979</v>
       </c>
       <c r="AJ6">
-        <v>0.01540391719523246</v>
+        <v>0.003185196420445926</v>
       </c>
       <c r="AK6">
-        <v>0.07429820137838292</v>
+        <v>0.0241009946442234</v>
       </c>
       <c r="AL6">
-        <v>5</v>
+        <v>6.73</v>
       </c>
       <c r="AM6">
-        <v>5</v>
+        <v>6.73</v>
       </c>
       <c r="AN6">
-        <v>1.532710280373832</v>
+        <v>1.062227074235808</v>
       </c>
       <c r="AO6">
-        <v>11.26</v>
+        <v>12.80832095096582</v>
       </c>
       <c r="AP6">
-        <v>0.6884735202492211</v>
+        <v>0.1375545851528384</v>
       </c>
       <c r="AQ6">
-        <v>11.26</v>
+        <v>12.80832095096582</v>
       </c>
     </row>
     <row r="7">
@@ -1228,7 +1228,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Religare Enterprises Limited (NSEI:RELIGARE)</t>
+          <t>Star Health and Allied Insurance Company Limited (NSEI:STARHEALTH)</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1236,23 +1236,29 @@
           <t>Insurance (Life)</t>
         </is>
       </c>
+      <c r="D7">
+        <v>0.317</v>
+      </c>
+      <c r="E7">
+        <v>0.5379999999999999</v>
+      </c>
       <c r="G7">
-        <v>-0.07227227227227227</v>
+        <v>0.07293936674785284</v>
       </c>
       <c r="H7">
-        <v>-0.07227227227227227</v>
+        <v>0.07293936674785284</v>
       </c>
       <c r="I7">
-        <v>0.05785785785785785</v>
+        <v>0.08124707301011014</v>
       </c>
       <c r="J7">
-        <v>0.05785785785785785</v>
+        <v>0.06084827918666346</v>
       </c>
       <c r="K7">
-        <v>-140.7</v>
+        <v>87.3</v>
       </c>
       <c r="L7">
-        <v>-0.2816816816816817</v>
+        <v>0.05595436482502243</v>
       </c>
       <c r="M7">
         <v>-0</v>
@@ -1261,7 +1267,7 @@
         <v>-0</v>
       </c>
       <c r="O7">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="P7">
         <v>-0</v>
@@ -1270,79 +1276,79 @@
         <v>-0</v>
       </c>
       <c r="R7">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="S7">
         <v>0</v>
       </c>
       <c r="U7">
-        <v>313.1</v>
+        <v>32.1</v>
       </c>
       <c r="V7">
-        <v>0.4614591009579956</v>
+        <v>0.008386237165922095</v>
       </c>
       <c r="W7">
-        <v>7.564516129032257</v>
+        <v>0.1085820895522388</v>
       </c>
       <c r="X7">
-        <v>0.1663162305863353</v>
+        <v>0.1002842032305827</v>
       </c>
       <c r="Y7">
-        <v>7.398199898445922</v>
+        <v>0.008297886321656067</v>
       </c>
       <c r="Z7">
-        <v>1.644227920603049</v>
+        <v>1.872558521946625</v>
       </c>
       <c r="AA7">
-        <v>0.09513150531617239</v>
+        <v>0.1139419637367741</v>
       </c>
       <c r="AB7">
-        <v>0.1144029313088499</v>
+        <v>0.09955923925633199</v>
       </c>
       <c r="AC7">
-        <v>-0.01927142599267749</v>
+        <v>0.01438272448044214</v>
       </c>
       <c r="AD7">
-        <v>617.1</v>
+        <v>56.6</v>
       </c>
       <c r="AE7">
-        <v>0</v>
+        <v>2.191583448130811</v>
       </c>
       <c r="AF7">
-        <v>617.1</v>
+        <v>58.79158344813082</v>
       </c>
       <c r="AG7">
-        <v>304</v>
+        <v>26.69158344813081</v>
       </c>
       <c r="AH7">
-        <v>0.4763044149428837</v>
+        <v>0.01512716088168404</v>
       </c>
       <c r="AI7">
-        <v>1.173416999429549</v>
+        <v>0.06785014946616633</v>
       </c>
       <c r="AJ7">
-        <v>0.3094147582697201</v>
+        <v>0.006924979694007265</v>
       </c>
       <c r="AK7">
-        <v>1.428571428571429</v>
+        <v>0.03198927695055073</v>
       </c>
       <c r="AL7">
-        <v>93.7</v>
+        <v>9.26</v>
       </c>
       <c r="AM7">
-        <v>93.7</v>
+        <v>9.26</v>
       </c>
       <c r="AN7">
-        <v>20.10097719869707</v>
+        <v>0.4414976599063962</v>
       </c>
       <c r="AO7">
-        <v>0.3084311632870864</v>
+        <v>13.59611231101512</v>
       </c>
       <c r="AP7">
-        <v>9.90228013029316</v>
+        <v>0.2082026790025804</v>
       </c>
       <c r="AQ7">
-        <v>0.3084311632870864</v>
+        <v>13.59611231101512</v>
       </c>
     </row>
     <row r="8">
@@ -1362,49 +1368,49 @@
         </is>
       </c>
       <c r="D8">
-        <v>0.0421</v>
+        <v>0.128</v>
       </c>
       <c r="E8">
-        <v>-0.127</v>
+        <v>-0.07969999999999999</v>
       </c>
       <c r="F8">
-        <v>0.126</v>
+        <v>0.034</v>
       </c>
       <c r="G8">
-        <v>0.02535803210369246</v>
+        <v>0.0178314121037464</v>
       </c>
       <c r="H8">
-        <v>0.02535803210369246</v>
+        <v>0.0178314121037464</v>
       </c>
       <c r="I8">
-        <v>0.0260739044736731</v>
+        <v>0.01759100351739927</v>
       </c>
       <c r="J8">
-        <v>0.01994444949187076</v>
+        <v>0.01407022348789047</v>
       </c>
       <c r="K8">
-        <v>105.1</v>
+        <v>109.2</v>
       </c>
       <c r="L8">
-        <v>0.01855939536279998</v>
+        <v>0.01311239193083574</v>
       </c>
       <c r="M8">
-        <v>9.710000000000001</v>
+        <v>10.4</v>
       </c>
       <c r="N8">
-        <v>0.001237794151390766</v>
+        <v>0.001130041724617524</v>
       </c>
       <c r="O8">
-        <v>0.09238820171265463</v>
+        <v>0.09523809523809523</v>
       </c>
       <c r="P8">
-        <v>9.710000000000001</v>
+        <v>10.4</v>
       </c>
       <c r="Q8">
-        <v>0.001237794151390766</v>
+        <v>0.001130041724617524</v>
       </c>
       <c r="R8">
-        <v>0.09238820171265463</v>
+        <v>0.09523809523809523</v>
       </c>
       <c r="S8">
         <v>0</v>
@@ -1413,73 +1419,73 @@
         <v>0</v>
       </c>
       <c r="U8">
-        <v>66.5</v>
+        <v>88.2</v>
       </c>
       <c r="V8">
-        <v>0.008477169007980012</v>
+        <v>0.009583623087621696</v>
       </c>
       <c r="W8">
-        <v>0.0891282225237449</v>
+        <v>0.09231549581536901</v>
       </c>
       <c r="X8">
-        <v>0.1177468123936177</v>
+        <v>0.1003022661662167</v>
       </c>
       <c r="Y8">
-        <v>-0.02861858986987276</v>
+        <v>-0.00798677035084773</v>
       </c>
       <c r="Z8">
-        <v>4.646537593256243</v>
+        <v>6.584645276642527</v>
       </c>
       <c r="AA8">
-        <v>0.09267263434077787</v>
+        <v>0.09264743063084273</v>
       </c>
       <c r="AB8">
-        <v>0.1165222121597169</v>
+        <v>0.09949409385958073</v>
       </c>
       <c r="AC8">
-        <v>-0.02384957781893904</v>
+        <v>-0.006846663228738004</v>
       </c>
       <c r="AD8">
-        <v>147.5</v>
+        <v>144.4</v>
       </c>
       <c r="AE8">
-        <v>1.235431780183103</v>
+        <v>0.8606135354946008</v>
       </c>
       <c r="AF8">
-        <v>148.7354317801831</v>
+        <v>145.2606135354946</v>
       </c>
       <c r="AG8">
-        <v>82.23543178018309</v>
+        <v>57.0606135354946</v>
       </c>
       <c r="AH8">
-        <v>0.01860743028358794</v>
+        <v>0.01553845275073138</v>
       </c>
       <c r="AI8">
-        <v>0.1116938076522548</v>
+        <v>0.1012508548467939</v>
       </c>
       <c r="AJ8">
-        <v>0.01037430794267353</v>
+        <v>0.006161879877558792</v>
       </c>
       <c r="AK8">
-        <v>0.06500128738349292</v>
+        <v>0.04237822700633374</v>
       </c>
       <c r="AL8">
-        <v>10.1</v>
+        <v>9.890000000000001</v>
       </c>
       <c r="AM8">
-        <v>10.1</v>
+        <v>9.890000000000001</v>
       </c>
       <c r="AN8">
-        <v>0.9646764900164158</v>
+        <v>0.948315492217771</v>
       </c>
       <c r="AO8">
-        <v>14.6039603960396</v>
+        <v>14.79271991911021</v>
       </c>
       <c r="AP8">
-        <v>0.537834492777569</v>
+        <v>0.3747331288861535</v>
       </c>
       <c r="AQ8">
-        <v>14.6039603960396</v>
+        <v>14.79271991911021</v>
       </c>
     </row>
     <row r="9">
@@ -1490,7 +1496,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Star Health and Allied Insurance Company Limited (NSEI:STARHEALTH)</t>
+          <t>HDFC Life Insurance Company Limited (NSEI:HDFCLIFE)</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1499,109 +1505,124 @@
         </is>
       </c>
       <c r="D9">
-        <v>0.379</v>
+        <v>0.225</v>
+      </c>
+      <c r="E9">
+        <v>0.038</v>
+      </c>
+      <c r="F9">
+        <v>0.07490000000000001</v>
       </c>
       <c r="G9">
-        <v>-0.1254994292237443</v>
+        <v>0.01742169944794296</v>
       </c>
       <c r="H9">
-        <v>-0.1254994292237443</v>
+        <v>0.01742169944794296</v>
       </c>
       <c r="I9">
-        <v>-0.0351288183764416</v>
+        <v>0.01055716038047142</v>
       </c>
       <c r="J9">
-        <v>-0.0351288183764416</v>
+        <v>0.01055716038047142</v>
       </c>
       <c r="K9">
-        <v>-43.5</v>
+        <v>178</v>
       </c>
       <c r="L9">
-        <v>-0.03103595890410959</v>
+        <v>0.01645999204741957</v>
       </c>
       <c r="M9">
-        <v>-0</v>
+        <v>49.4661</v>
       </c>
       <c r="N9">
-        <v>-0</v>
+        <v>0.002951244250079052</v>
       </c>
       <c r="O9">
-        <v>0</v>
+        <v>0.2778994382022472</v>
       </c>
       <c r="P9">
-        <v>-0</v>
+        <v>49.4661</v>
       </c>
       <c r="Q9">
-        <v>-0</v>
+        <v>0.002951244250079052</v>
       </c>
       <c r="R9">
-        <v>0</v>
+        <v>0.2778994382022472</v>
       </c>
       <c r="S9">
         <v>0</v>
       </c>
+      <c r="T9">
+        <v>0</v>
+      </c>
       <c r="U9">
-        <v>36.9</v>
+        <v>59</v>
       </c>
       <c r="V9">
-        <v>0.009274619212788418</v>
+        <v>0.003520055366294575</v>
+      </c>
+      <c r="W9">
+        <v>0.08132309941520467</v>
       </c>
       <c r="X9">
-        <v>0.1176213504289768</v>
+        <v>0.09992644575530411</v>
+      </c>
+      <c r="Y9">
+        <v>-0.01860334634009944</v>
       </c>
       <c r="Z9">
-        <v>588.2256211738376</v>
+        <v>4.816072061709767</v>
       </c>
       <c r="AA9">
-        <v>-20.66367101058528</v>
+        <v>0.05084404515937769</v>
       </c>
       <c r="AB9">
-        <v>0.1166332749371387</v>
+        <v>0.09956966413799391</v>
       </c>
       <c r="AC9">
-        <v>-20.78030428552242</v>
+        <v>-0.04872561897861622</v>
       </c>
       <c r="AD9">
-        <v>63.9</v>
+        <v>114.3</v>
       </c>
       <c r="AE9">
-        <v>2.382759182102656</v>
+        <v>2.319059647719816</v>
       </c>
       <c r="AF9">
-        <v>66.28275918210265</v>
+        <v>116.6190596477198</v>
       </c>
       <c r="AG9">
-        <v>29.38275918210265</v>
+        <v>57.61905964771981</v>
       </c>
       <c r="AH9">
-        <v>0.0163868183896399</v>
+        <v>0.006909645742743744</v>
       </c>
       <c r="AI9">
-        <v>0.07616232595989333</v>
+        <v>0.06624505626010244</v>
       </c>
       <c r="AJ9">
-        <v>0.007331059275339474</v>
+        <v>0.003425888704328395</v>
       </c>
       <c r="AK9">
-        <v>0.03525721987690199</v>
+        <v>0.03386529574886148</v>
       </c>
       <c r="AL9">
-        <v>8.31</v>
+        <v>7.91</v>
       </c>
       <c r="AM9">
-        <v>8.31</v>
+        <v>7.91</v>
       </c>
       <c r="AN9">
-        <v>-1.324077911313717</v>
+        <v>0.9578479845805747</v>
       </c>
       <c r="AO9">
-        <v>-6.040914560770156</v>
+        <v>14.3109987357775</v>
       </c>
       <c r="AP9">
-        <v>-0.6088429171591929</v>
+        <v>0.482854769527527</v>
       </c>
       <c r="AQ9">
-        <v>-6.040914560770156</v>
+        <v>14.3109987357775</v>
       </c>
     </row>
   </sheetData>
